--- a/LISTA DE PEÇAS POR MÁQUINA - TESTE.xlsx
+++ b/LISTA DE PEÇAS POR MÁQUINA - TESTE.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\git\pcmauro\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zeluzjunior\PycharmProjects\teste_visual\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3189C3A9-71B2-4C67-8212-57C06D9D4A30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89E70059-FDB2-42D1-AAF8-E1DC9402D61F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="195" yWindow="480" windowWidth="28605" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1950" yWindow="1950" windowWidth="21600" windowHeight="11835" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DADOS" sheetId="2" r:id="rId1"/>
@@ -3512,12 +3512,13 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="6dbcbc56-3d12-411a-a735-f36ec8e8bfd2">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3750,19 +3751,20 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="6dbcbc56-3d12-411a-a735-f36ec8e8bfd2">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A07255AE-BBDF-48D2-933F-8224645FB75F}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8B09F593-B1EE-43C0-8142-911C68E497CA}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="6dbcbc56-3d12-411a-a735-f36ec8e8bfd2"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -3787,11 +3789,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8B09F593-B1EE-43C0-8142-911C68E497CA}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A07255AE-BBDF-48D2-933F-8224645FB75F}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="6dbcbc56-3d12-411a-a735-f36ec8e8bfd2"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>